--- a/data_lake/industry/CFM/Index.xlsx
+++ b/data_lake/industry/CFM/Index.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\industry\CFM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04FAA5DE-2859-49D1-926E-1C1B3FF5C22F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71B38491-EB24-40BA-8FAB-E50E1B914425}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Index" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="118">
   <si>
     <t>Flash Wafer</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -1497,6 +1497,9 @@
                 <c:pt idx="289">
                   <c:v>46217</c:v>
                 </c:pt>
+                <c:pt idx="290">
+                  <c:v>46224</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2374,6 +2377,9 @@
                   <c:v>4018.5</c:v>
                 </c:pt>
                 <c:pt idx="289">
+                  <c:v>4059.66</c:v>
+                </c:pt>
+                <c:pt idx="290">
                   <c:v>4059.66</c:v>
                 </c:pt>
               </c:numCache>
@@ -3288,6 +3294,9 @@
                 <c:pt idx="289">
                   <c:v>46217</c:v>
                 </c:pt>
+                <c:pt idx="290">
+                  <c:v>46224</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4166,6 +4175,9 @@
                 </c:pt>
                 <c:pt idx="289">
                   <c:v>2991.37</c:v>
+                </c:pt>
+                <c:pt idx="290">
+                  <c:v>2988.98</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5242,7 +5254,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB1C738F-C0D7-48DA-9F8D-241372DE5FE0}">
-  <dimension ref="A1:Y291"/>
+  <dimension ref="A1:Y292"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="11.69921875" style="12" customWidth="1"/>
@@ -15614,6 +15626,26 @@
       </c>
       <c r="F291" s="19">
         <v>2991.37</v>
+      </c>
+    </row>
+    <row r="292" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A292" s="12">
+        <v>46224</v>
+      </c>
+      <c r="B292" s="12">
+        <v>46224</v>
+      </c>
+      <c r="C292" s="13">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D292" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="E292" s="19">
+        <v>4059.66</v>
+      </c>
+      <c r="F292" s="19">
+        <v>2988.98</v>
       </c>
     </row>
   </sheetData>

--- a/data_lake/industry/CFM/Index.xlsx
+++ b/data_lake/industry/CFM/Index.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\industry\CFM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71B38491-EB24-40BA-8FAB-E50E1B914425}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9B6FB0B-1E0C-4A58-9BCE-05B6E62E13FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Index" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="118">
   <si>
     <t>Flash Wafer</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -1500,6 +1500,12 @@
                 <c:pt idx="290">
                   <c:v>46224</c:v>
                 </c:pt>
+                <c:pt idx="291">
+                  <c:v>46231</c:v>
+                </c:pt>
+                <c:pt idx="292">
+                  <c:v>46238</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2381,6 +2387,12 @@
                 </c:pt>
                 <c:pt idx="290">
                   <c:v>4059.66</c:v>
+                </c:pt>
+                <c:pt idx="291">
+                  <c:v>4061.45</c:v>
+                </c:pt>
+                <c:pt idx="292">
+                  <c:v>4105.1899999999996</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3297,6 +3309,12 @@
                 <c:pt idx="290">
                   <c:v>46224</c:v>
                 </c:pt>
+                <c:pt idx="291">
+                  <c:v>46231</c:v>
+                </c:pt>
+                <c:pt idx="292">
+                  <c:v>46238</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -4178,6 +4196,12 @@
                 </c:pt>
                 <c:pt idx="290">
                   <c:v>2988.98</c:v>
+                </c:pt>
+                <c:pt idx="291">
+                  <c:v>2988.98</c:v>
+                </c:pt>
+                <c:pt idx="292">
+                  <c:v>2987.73</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5254,7 +5278,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB1C738F-C0D7-48DA-9F8D-241372DE5FE0}">
-  <dimension ref="A1:Y292"/>
+  <dimension ref="A1:Y294"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="11.69921875" style="12" customWidth="1"/>
@@ -15646,6 +15670,46 @@
       </c>
       <c r="F292" s="19">
         <v>2988.98</v>
+      </c>
+    </row>
+    <row r="293" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A293" s="12">
+        <v>46231</v>
+      </c>
+      <c r="B293" s="12">
+        <v>46231</v>
+      </c>
+      <c r="C293" s="13">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D293" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="E293" s="19">
+        <v>4061.45</v>
+      </c>
+      <c r="F293" s="19">
+        <v>2988.98</v>
+      </c>
+    </row>
+    <row r="294" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A294" s="12">
+        <v>46238</v>
+      </c>
+      <c r="B294" s="12">
+        <v>46238</v>
+      </c>
+      <c r="C294" s="13">
+        <v>0.45833333333333298</v>
+      </c>
+      <c r="D294" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="E294" s="19">
+        <v>4105.1899999999996</v>
+      </c>
+      <c r="F294" s="19">
+        <v>2987.73</v>
       </c>
     </row>
   </sheetData>
